--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484538_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484538_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3114</v>
+        <v>1.9353</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1477</v>
+        <v>-0.5734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4591</v>
+        <v>2.5086</v>
       </c>
       <c r="G2" t="n">
         <v>-0.08740000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8649</v>
+        <v>1.4887</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1343</v>
+        <v>0.7085</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7306</v>
+        <v>0.7801</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>P. GARCIA BOSCH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5287</v>
+        <v>1.4798</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8323</v>
+        <v>1.0709</v>
       </c>
       <c r="F3" t="n">
-        <v>2.361</v>
+        <v>0.4089</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8379</v>
+        <v>0.5884</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8225</v>
+        <v>1.7104</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9846</v>
+        <v>-1.122</v>
       </c>
       <c r="J3" t="n">
-        <v>2.02</v>
+        <v>1.1671</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9783</v>
+        <v>1.8082</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0417</v>
+        <v>-0.641</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1821</v>
+        <v>-0.5787</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1558</v>
+        <v>-0.0977</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0262</v>
+        <v>-0.481</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1154</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2986</v>
+        <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4971</v>
+        <v>0.7741</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2527</v>
+        <v>0.4981</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2445</v>
+        <v>0.276</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0104</v>
+        <v>-0.2492</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0104</v>
+        <v>0.3219</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GARCIA BOSCH</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0431</v>
+        <v>1.2458</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5351</v>
+        <v>-1.0657</v>
       </c>
       <c r="F4" t="n">
-        <v>0.508</v>
+        <v>2.3115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5884</v>
+        <v>0.8379</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7104</v>
+        <v>1.8225</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.122</v>
+        <v>-0.9846</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1671</v>
+        <v>2.02</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8082</v>
+        <v>1.9783</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.641</v>
+        <v>0.0417</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5787</v>
+        <v>-1.1821</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0977</v>
+        <v>-0.1558</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.481</v>
+        <v>-1.0262</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-3.1154</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2828</v>
+        <v>3.2986</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3374</v>
+        <v>0.2142</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0377</v>
+        <v>0.0193</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3751</v>
+        <v>0.1949</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2492</v>
+        <v>0.0104</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MUNOZ TORREGROSA</t>
+          <t>D. MUÑOZ TORREGROSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6821</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2768</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4053</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3296</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8486</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.481</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8394</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8394</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4902</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0092</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.481</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2341</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1162</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1179</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MUÑOZ TORREGROSA</t>
+          <t>D. MUNOZ TORREGROSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>0.2127</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>-0.3412</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>-1.3296</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-0.8486</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.481</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>-0.8394</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>-0.8394</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.4902</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.0092</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.481</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.7647</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.4981</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0042</v>
+        <v>0.1718</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9619</v>
+        <v>-0.7696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9661</v>
+        <v>0.9414</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4708</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2399</v>
+        <v>0.4074</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1659</v>
+        <v>0.0264</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4058</v>
+        <v>0.381</v>
       </c>
       <c r="V7" t="n">
         <v>0.6854</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5709</v>
+        <v>-0.1457</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0826</v>
+        <v>-1.7081</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5117</v>
+        <v>1.5624</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.719</v>
+        <v>-0.844</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3053</v>
+        <v>1.4544</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.4137</v>
+        <v>-2.2985</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.4589</v>
+        <v>-0.2315</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0184</v>
+        <v>1.6499</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.4773</v>
+        <v>-1.8814</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.26</v>
+        <v>-0.6125</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3237</v>
+        <v>-0.1955</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.417</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2828</v>
+        <v>-2.1991</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2986</v>
+        <v>2.5656</v>
       </c>
       <c r="S8" t="n">
-        <v>0.803</v>
+        <v>-0.042</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1252</v>
+        <v>0.089</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6778</v>
+        <v>-0.1311</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3293</v>
+        <v>0.3738</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5339</v>
+        <v>0.6335</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2047</v>
+        <v>-0.2596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7037</v>
+        <v>-0.9206</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0927</v>
+        <v>-2.9864</v>
       </c>
       <c r="F9" t="n">
-        <v>1.389</v>
+        <v>2.0658</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.844</v>
+        <v>-4.719</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4544</v>
+        <v>-0.3053</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2985</v>
+        <v>-4.4137</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2315</v>
+        <v>-4.4589</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6499</v>
+        <v>0.0184</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8814</v>
+        <v>-4.4773</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6125</v>
+        <v>-0.26</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1955</v>
+        <v>-0.3237</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.417</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>2.0158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1991</v>
+        <v>-1.2828</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5656</v>
+        <v>3.2986</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6001</v>
+        <v>0.4532</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2956</v>
+        <v>0.2214</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3045</v>
+        <v>0.2319</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3738</v>
+        <v>1.3293</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6335</v>
+        <v>2.5339</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2596</v>
+        <v>-1.2047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2311</v>
+        <v>-2.3994</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4185</v>
+        <v>-4.66</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1874</v>
+        <v>2.2606</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0161</v>
+        <v>-1.2997</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5351</v>
+        <v>-0.3317</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.481</v>
+        <v>-0.9681</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0784</v>
+        <v>-1.5696</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4373</v>
+        <v>-0.3133</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.641</v>
+        <v>-1.2563</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0623</v>
+        <v>0.2698</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0977</v>
+        <v>-0.0184</v>
       </c>
       <c r="O10" t="n">
-        <v>0.16</v>
+        <v>0.2882</v>
       </c>
       <c r="P10" t="n">
-        <v>0.733</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2828</v>
+        <v>-3.1154</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0158</v>
+        <v>2.9321</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3634</v>
+        <v>0.6725</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2542</v>
+        <v>0.0249</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1093</v>
+        <v>0.6476</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3115</v>
+        <v>-1.5889</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7155</v>
+        <v>-2.591</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8523</v>
+        <v>-4.8031</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1368</v>
+        <v>2.2122</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2997</v>
+        <v>-3.0161</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3317</v>
+        <v>-2.5351</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9681</v>
+        <v>-0.481</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5696</v>
+        <v>-3.0784</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3133</v>
+        <v>-2.4373</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2563</v>
+        <v>-0.641</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2698</v>
+        <v>0.0623</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0184</v>
+        <v>-0.0977</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2882</v>
+        <v>0.16</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1154</v>
+        <v>-1.2828</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9321</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3563</v>
+        <v>0.0036</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1674</v>
+        <v>-0.1304</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5889</v>
+        <v>-0.3115</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9231</v>
+        <v>-2.6232</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6949</v>
+        <v>-2.5437</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2282</v>
+        <v>-0.0796</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2778</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0668</v>
+        <v>0.233</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0166</v>
+        <v>0.1678</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0834</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.3219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6304</v>
+        <v>-3.2953</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8062</v>
+        <v>-1.4216</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8241</v>
+        <v>-1.8737</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5209</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.486</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6976</v>
+        <v>-0.313</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1235</v>
+        <v>-0.1731</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2047</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.880100000000001</v>
+        <v>-6.604700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.7521</v>
+        <v>-19.4768</v>
       </c>
       <c r="F14" t="n">
         <v>12.8721</v>
@@ -1513,7 +1513,7 @@
         <v>-17.8139</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7787999999999999</v>
+        <v>0.7788000000000004</v>
       </c>
       <c r="I14" t="n">
         <v>-18.593</v>
@@ -1522,7 +1522,7 @@
         <v>-11.6969</v>
       </c>
       <c r="K14" t="n">
-        <v>2.245200000000001</v>
+        <v>2.245199999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-13.9419</v>
@@ -1546,16 +1546,16 @@
         <v>20.1581</v>
       </c>
       <c r="S14" t="n">
-        <v>4.208100000000001</v>
+        <v>4.4834</v>
       </c>
       <c r="T14" t="n">
-        <v>1.535</v>
+        <v>1.8101</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6733</v>
+        <v>2.6731</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3115999999999997</v>
+        <v>0.3116000000000003</v>
       </c>
       <c r="W14" t="n">
         <v>4.153999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.447</v>
+        <v>7.5519</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5935</v>
+        <v>4.6896</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8536</v>
+        <v>2.8623</v>
       </c>
       <c r="G15" t="n">
         <v>3.5354</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3658</v>
+        <v>-0.2609</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3137</v>
+        <v>-0.2175</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0521</v>
+        <v>-0.0434</v>
       </c>
       <c r="V15" t="n">
         <v>3.1778</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8461</v>
+        <v>2.6314</v>
       </c>
       <c r="E16" t="n">
         <v>0.675</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1711</v>
+        <v>1.9564</v>
       </c>
       <c r="G16" t="n">
         <v>1.5732</v>
@@ -1702,13 +1702,13 @@
         <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5596</v>
+        <v>-0.7743</v>
       </c>
       <c r="T16" t="n">
         <v>-0.497</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0627</v>
+        <v>-0.2774</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>C. WITSON DEAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5983000000000001</v>
+        <v>1.3019</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.5238</v>
+        <v>-2.5868</v>
       </c>
       <c r="F17" t="n">
-        <v>4.1221</v>
+        <v>3.8887</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5111</v>
+        <v>1.8053</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1296</v>
+        <v>-0.8619</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3814</v>
+        <v>2.6672</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6897</v>
+        <v>-0.3863</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5327</v>
+        <v>-1.1303</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.157</v>
+        <v>0.7441</v>
       </c>
       <c r="M17" t="n">
-        <v>2.2008</v>
+        <v>2.1916</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6623</v>
+        <v>0.2685</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5385</v>
+        <v>1.9231</v>
       </c>
       <c r="P17" t="n">
         <v>-0.5498</v>
@@ -1780,13 +1780,13 @@
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>0.637</v>
+        <v>0.0464</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0015</v>
+        <v>-0.368</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6385</v>
+        <v>0.4144</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4875</v>
+        <v>1.0703</v>
       </c>
       <c r="E18" t="n">
         <v>0.3257</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1618</v>
+        <v>0.7446</v>
       </c>
       <c r="G18" t="n">
         <v>2.5651</v>
@@ -1858,13 +1858,13 @@
         <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1326</v>
+        <v>-0.5498</v>
       </c>
       <c r="T18" t="n">
         <v>-0.5505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5821</v>
+        <v>0.0007</v>
       </c>
       <c r="V18" t="n">
         <v>-0.945</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1714</v>
+        <v>0.977</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0925</v>
+        <v>-2.8041</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2639</v>
+        <v>3.7811</v>
       </c>
       <c r="G19" t="n">
         <v>2.7103</v>
@@ -1936,13 +1936,13 @@
         <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7772</v>
+        <v>0.0285</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.644</v>
+        <v>-0.3555</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1332</v>
+        <v>0.384</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5785</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0423</v>
+        <v>0.8043</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9204</v>
+        <v>-2.8242</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9627</v>
+        <v>3.6285</v>
       </c>
       <c r="G20" t="n">
         <v>3.6351</v>
@@ -2014,13 +2014,13 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7889</v>
+        <v>-0.027</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4419</v>
+        <v>-0.3458</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.347</v>
+        <v>0.3188</v>
       </c>
       <c r="V20" t="n">
         <v>0.3115</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. WITSON DEAN</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0123</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9715</v>
+        <v>-3.6199</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9591</v>
+        <v>4.2051</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8053</v>
+        <v>0.5111</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8619</v>
+        <v>0.1296</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6672</v>
+        <v>0.3814</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3863</v>
+        <v>-1.6897</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1303</v>
+        <v>-0.5327</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7441</v>
+        <v>-1.157</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1916</v>
+        <v>2.2008</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2685</v>
+        <v>0.6623</v>
       </c>
       <c r="O21" t="n">
-        <v>1.9231</v>
+        <v>1.5385</v>
       </c>
       <c r="P21" t="n">
         <v>-0.5498</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2679</v>
+        <v>0.6239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7526</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5152</v>
+        <v>0.7215</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1643</v>
+        <v>-1.0712</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5472</v>
+        <v>-1.3226</v>
       </c>
       <c r="F22" t="n">
-        <v>3.3828</v>
+        <v>0.2515</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4669</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.501</v>
+        <v>0.184</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9679</v>
+        <v>0.7661</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0728</v>
+        <v>0.8403</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7651</v>
+        <v>0.7153</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3076</v>
+        <v>0.125</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5397</v>
+        <v>0.1098</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7359</v>
+        <v>-0.5312</v>
       </c>
       <c r="O22" t="n">
-        <v>2.2756</v>
+        <v>0.641</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.4819</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.7647</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5391</v>
+        <v>-0.2332</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9684</v>
+        <v>-0.3303</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5708</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0104</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2532</v>
+        <v>-1.2332</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3226</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0694</v>
+        <v>-1.1447</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.0613</v>
       </c>
       <c r="H23" t="n">
-        <v>0.184</v>
+        <v>-0.1951</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7661</v>
+        <v>0.2564</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8403</v>
+        <v>0.0217</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7153</v>
+        <v>0.0217</v>
       </c>
       <c r="L23" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1098</v>
+        <v>0.0397</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5312</v>
+        <v>-0.2167</v>
       </c>
       <c r="O23" t="n">
-        <v>0.641</v>
+        <v>0.2564</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4153</v>
+        <v>-0.0275</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3303</v>
+        <v>-0.1101</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2827</v>
+        <v>-1.8914</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-5.3164</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1943</v>
+        <v>3.425</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0613</v>
+        <v>0.4669</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1951</v>
+        <v>-1.501</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2564</v>
+        <v>1.9679</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0217</v>
+        <v>-1.0728</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0217</v>
+        <v>-0.7651</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.3076</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0397</v>
+        <v>1.5397</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2167</v>
+        <v>-0.7359</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2564</v>
+        <v>2.2756</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-3.4819</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-4.7647</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0771</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1101</v>
+        <v>0.1991</v>
       </c>
       <c r="U24" t="n">
-        <v>0.033</v>
+        <v>0.6129</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.267</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.880100000000002</v>
+        <v>10.7262</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.8722</v>
+        <v>-12.8721</v>
       </c>
       <c r="F25" t="n">
-        <v>19.7522</v>
+        <v>23.5985</v>
       </c>
       <c r="G25" t="n">
         <v>17.8138</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7792000000000001</v>
+        <v>-0.7791999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>18.5928</v>
@@ -2383,7 +2383,7 @@
         <v>1.4661</v>
       </c>
       <c r="L25" t="n">
-        <v>4.651</v>
+        <v>4.651000000000001</v>
       </c>
       <c r="M25" t="n">
         <v>11.697</v>
@@ -2404,22 +2404,22 @@
         <v>13.7443</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.2083</v>
+        <v>-0.3619000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-2.6732</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.535</v>
+        <v>2.3112</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3115999999999997</v>
+        <v>-0.3115999999999998</v>
       </c>
       <c r="W25" t="n">
         <v>3.8425</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.154</v>
+        <v>-4.153999999999999</v>
       </c>
     </row>
   </sheetData>
